--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{C932B189-2194-7C46-A38E-8BF477188C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{B42189F5-93C7-0B41-961E-2C6C8B23473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urls" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>urls_geral</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>http://m3u4u.com/m3u/m/d7148k492ns4kvvpwj5v</t>
+  </si>
+  <si>
+    <t>Our Vinyl</t>
   </si>
 </sst>
 </file>
@@ -743,7 +746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -979,6 +982,11 @@
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{B42189F5-93C7-0B41-961E-2C6C8B23473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{4B9319C8-21FE-8945-A972-B42DBF83ED37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="urls" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="68">
   <si>
     <t>urls_geral</t>
   </si>
@@ -55,42 +55,6 @@
     <t>https://i.mjh.nz/Stirr/all.m3u8</t>
   </si>
   <si>
-    <t>https://iptv-org.github.io/iptv/categories/music.m3u</t>
-  </si>
-  <si>
-    <t>https://iptv-org.github.io/iptv/index.m3u</t>
-  </si>
-  <si>
-    <t>https://lib.bz/br.m3u</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/helenfernanda/gratis/main/iptvlegal.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/klowd.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/lg.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/localnow.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/rakuten.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/redbox.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/tcl.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/tubi.m3u</t>
-  </si>
-  <si>
-    <t>https://www.apsattv.com/vizio.m3u</t>
-  </si>
-  <si>
     <t>canais</t>
   </si>
   <si>
@@ -230,9 +194,6 @@
   </si>
   <si>
     <t>Yo! MTV Raps Classic</t>
-  </si>
-  <si>
-    <t>http://m3u4u.com/m3u/m/d7148k492ns4kvvpwj5v</t>
   </si>
   <si>
     <t>Our Vinyl</t>
@@ -288,12 +249,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -629,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultColWidth="8.47265625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="128.3359375" customWidth="1"/>
@@ -670,75 +630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A11" r:id="rId1" xr:uid="{4457D92F-5B0D-3F42-94D3-ED22FBE51341}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -751,242 +643,242 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\melhorias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F155EEE0-A49A-4F79-B9CB-96E10C250D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65B257E-1A7B-4AD9-9A49-0897D828A2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5568" yWindow="2808" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -379,12 +379,6 @@
     <t>merged+3</t>
   </si>
   <si>
-    <t>nas nuvens</t>
-  </si>
-  <si>
-    <t>http://m3u4u.com/m3u/m/4me1pvz5m2twn99p9y36</t>
-  </si>
-  <si>
     <t>prime+git</t>
   </si>
   <si>
@@ -410,6 +404,18 @@
   </si>
   <si>
     <t>reduced.m3u8</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/m/w5798zzzz1hzxw38k4n1</t>
+  </si>
+  <si>
+    <t>merged+4</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/3m97ypeg3qf53gq4ndxq</t>
+  </si>
+  <si>
+    <t>sports-git</t>
   </si>
 </sst>
 </file>
@@ -868,37 +874,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +978,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1009,13 +1015,21 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -1428,7 +1442,7 @@
     <sortCondition ref="A2:A42"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65B257E-1A7B-4AD9-9A49-0897D828A2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6717C5-3D16-4046-B85B-A7E726C1DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5568" yWindow="2808" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduced.m3u8" sheetId="6" r:id="rId1"/>
-    <sheet name="xml_reduced" sheetId="7" r:id="rId2"/>
+    <sheet name="xml_full" sheetId="4" r:id="rId2"/>
     <sheet name="full.m3u8" sheetId="3" r:id="rId3"/>
-    <sheet name="xml_full" sheetId="4" r:id="rId4"/>
-    <sheet name="canais" sheetId="5" r:id="rId5"/>
+    <sheet name="canais" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="156">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -416,13 +415,94 @@
   </si>
   <si>
     <t>sports-git</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/DStv/za.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/MeTV/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/Optus/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/PBS/all.m3u8</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/PBS/kids_all.m3u8</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/PBS/kids_all.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/PBS/all.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/Singtel/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/SkyGo/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/SkySportNow/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/all/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/all/raw.m3u8</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/nz/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/nz/raw.m3u8</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/nzau/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/nzau/raw.m3u8</t>
+  </si>
+  <si>
+    <t>fonte</t>
+  </si>
+  <si>
+    <t>obs</t>
+  </si>
+  <si>
+    <t>nas nuvens</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/jq2zy914zghw15q6yxr5</t>
+  </si>
+  <si>
+    <t>https://lib.bz</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/jwmzn18r49fk9jd2y721</t>
+  </si>
+  <si>
+    <t>https://u.m3uiptv.com/wp-content/plugins/download-attachments/includes/download.php?id=HyR3nGtbSkqOv4WMBn4wMQ</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/5g28ne1gjpsvdwk5nzpe</t>
+  </si>
+  <si>
+    <t>https://u.m3uiptv.com/wp-content/plugins/download-attachments/includes/download.php?id=M93Oz32LSBA8sx4v7xOR5g</t>
+  </si>
+  <si>
+    <t>hotmail</t>
+  </si>
+  <si>
+    <t>http://m3u4u.com/m3u/p87vnrz685f46xr5n41j</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -444,14 +524,6 @@
       <name val="Inherit"/>
       <charset val="1"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -470,21 +542,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Hyperlink 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -866,10 +935,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FB9D2C-6B3A-4651-B005-4FD4521E69BD}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -905,6 +974,31 @@
     <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -913,8 +1007,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B22B5A-28AE-4CEA-B703-E41D244694DB}">
-  <dimension ref="A1:A25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="60.5546875" customWidth="1"/>
@@ -927,36 +1021,203 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="3"/>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -980,6 +1241,12 @@
       <c r="A1" t="s">
         <v>123</v>
       </c>
+      <c r="B1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
@@ -1028,8 +1295,52 @@
       <c r="A7" t="s">
         <v>127</v>
       </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
       <c r="C7" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -1451,174 +1762,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A30"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="60.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPágina &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A78"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6717C5-3D16-4046-B85B-A7E726C1DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBC97F4-7A4A-4DAD-838F-67FD1417C23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduced.m3u8" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="152">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -426,12 +426,6 @@
     <t>https://i.mjh.nz/Optus/epg.xml</t>
   </si>
   <si>
-    <t>https://i.mjh.nz/PBS/all.m3u8</t>
-  </si>
-  <si>
-    <t>https://i.mjh.nz/PBS/kids_all.m3u8</t>
-  </si>
-  <si>
     <t>https://i.mjh.nz/PBS/kids_all.xml</t>
   </si>
   <si>
@@ -450,13 +444,7 @@
     <t>https://i.mjh.nz/all/epg.xml</t>
   </si>
   <si>
-    <t>https://i.mjh.nz/all/raw.m3u8</t>
-  </si>
-  <si>
     <t>https://i.mjh.nz/nz/epg.xml</t>
-  </si>
-  <si>
-    <t>https://i.mjh.nz/nz/raw.m3u8</t>
   </si>
   <si>
     <t>https://i.mjh.nz/nzau/epg.xml</t>
@@ -935,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FB9D2C-6B3A-4651-B005-4FD4521E69BD}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
@@ -978,27 +966,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1181,42 +1149,42 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1242,10 +1210,10 @@
         <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1296,7 +1264,7 @@
         <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
         <v>128</v>
@@ -1304,43 +1272,43 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
         <v>147</v>
-      </c>
-      <c r="C9" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:1">

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBC97F4-7A4A-4DAD-838F-67FD1417C23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6717C5-3D16-4046-B85B-A7E726C1DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduced.m3u8" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="156">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -426,6 +426,12 @@
     <t>https://i.mjh.nz/Optus/epg.xml</t>
   </si>
   <si>
+    <t>https://i.mjh.nz/PBS/all.m3u8</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/PBS/kids_all.m3u8</t>
+  </si>
+  <si>
     <t>https://i.mjh.nz/PBS/kids_all.xml</t>
   </si>
   <si>
@@ -444,7 +450,13 @@
     <t>https://i.mjh.nz/all/epg.xml</t>
   </si>
   <si>
+    <t>https://i.mjh.nz/all/raw.m3u8</t>
+  </si>
+  <si>
     <t>https://i.mjh.nz/nz/epg.xml</t>
+  </si>
+  <si>
+    <t>https://i.mjh.nz/nz/raw.m3u8</t>
   </si>
   <si>
     <t>https://i.mjh.nz/nzau/epg.xml</t>
@@ -923,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FB9D2C-6B3A-4651-B005-4FD4521E69BD}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
@@ -966,7 +978,27 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1149,42 +1181,42 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1210,10 +1242,10 @@
         <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1264,7 +1296,7 @@
         <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
         <v>128</v>
@@ -1272,43 +1304,43 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:1">

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6717C5-3D16-4046-B85B-A7E726C1DCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDC76F6-0869-4ECF-8F8A-F914DE791F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4164" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7400" yWindow="1420" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduced.m3u8" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -424,12 +424,6 @@
   </si>
   <si>
     <t>https://i.mjh.nz/Optus/epg.xml</t>
-  </si>
-  <si>
-    <t>https://i.mjh.nz/PBS/all.m3u8</t>
-  </si>
-  <si>
-    <t>https://i.mjh.nz/PBS/kids_all.m3u8</t>
   </si>
   <si>
     <t>https://i.mjh.nz/PBS/kids_all.xml</t>
@@ -639,9 +633,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -679,7 +673,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -785,7 +779,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -927,7 +921,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -935,10 +929,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FB9D2C-6B3A-4651-B005-4FD4521E69BD}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -948,60 +942,53 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A10">
+    <sortCondition ref="A2:A10"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -1009,9 +996,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="60.5546875" customWidth="1"/>
+    <col min="1" max="1" width="60.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1181,42 +1168,42 @@
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1232,9 +1219,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C411"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="108.33203125" customWidth="1"/>
+    <col min="1" max="1" width="108.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1229,10 @@
         <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1296,7 +1283,7 @@
         <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
         <v>128</v>
@@ -1304,43 +1291,43 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" t="s">
         <v>147</v>
-      </c>
-      <c r="C8" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" t="s">
         <v>152</v>
       </c>
-      <c r="B10" t="s">
-        <v>154</v>
-      </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -1764,9 +1751,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A78"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">

--- a/urls_geral.xlsx
+++ b/urls_geral.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\thestreamremainsthesame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDC76F6-0869-4ECF-8F8A-F914DE791F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D187593F-B0DF-4A78-9CB0-8B4FF2704752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="1420" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reduced.m3u8" sheetId="6" r:id="rId1"/>
-    <sheet name="xml_full" sheetId="4" r:id="rId2"/>
-    <sheet name="full.m3u8" sheetId="3" r:id="rId3"/>
-    <sheet name="canais" sheetId="5" r:id="rId4"/>
+    <sheet name="xml_reduced" sheetId="7" r:id="rId2"/>
+    <sheet name="xml_full" sheetId="4" r:id="rId3"/>
+    <sheet name="full.m3u8" sheetId="3" r:id="rId4"/>
+    <sheet name="canais" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="157">
   <si>
     <t>https://i.mjh.nz/Plex/all.xml</t>
   </si>
@@ -120,9 +121,6 @@
     <t>canais</t>
   </si>
   <si>
-    <t>4Music</t>
-  </si>
-  <si>
     <t>AMusic</t>
   </si>
   <si>
@@ -490,6 +488,18 @@
   </si>
   <si>
     <t>http://m3u4u.com/m3u/p87vnrz685f46xr5n41j</t>
+  </si>
+  <si>
+    <t>xml_reduced</t>
+  </si>
+  <si>
+    <t>BLITS TV</t>
+  </si>
+  <si>
+    <t>Vh1</t>
+  </si>
+  <si>
+    <t>4Mu+A80+A2:A80</t>
   </si>
 </sst>
 </file>
@@ -937,52 +947,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -994,6 +1004,72 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D67087-6A29-4143-8B8B-73E5B596A26F}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="34.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A10">
+    <sortCondition ref="A2:A10"/>
+  </sortState>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5"/>
@@ -1123,7 +1199,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -1153,57 +1229,57 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1216,7 +1292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C411"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5"/>
@@ -1226,108 +1302,108 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
         <v>109</v>
-      </c>
-      <c r="B3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
         <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
         <v>125</v>
       </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
         <v>127</v>
-      </c>
-      <c r="B7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" t="s">
         <v>146</v>
-      </c>
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
         <v>148</v>
-      </c>
-      <c r="B9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -1748,9 +1824,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
@@ -1763,57 +1839,57 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -1823,330 +1899,343 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A80">
+    <sortCondition ref="A2:A80"/>
+  </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
